--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D3">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H3">
         <v>426</v>
